--- a/tabular/sublineage/herv_sublineage_alias.xlsx
+++ b/tabular/sublineage/herv_sublineage_alias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C15F77-09CD-CD45-BE87-F568B33BC655}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DBA516-268B-8947-A5FA-F2AD9F6854A5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1980" yWindow="500" windowWidth="26820" windowHeight="15940" xr2:uid="{E2A31913-0241-5047-ACED-7542084468C7}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="122">
   <si>
     <t>erv_lineage.id</t>
   </si>
@@ -68,21 +68,6 @@
     <t>ERVL-B4</t>
   </si>
   <si>
-    <t>ERV-Le</t>
-  </si>
-  <si>
-    <t>ERVL-E</t>
-  </si>
-  <si>
-    <t>HERV-1</t>
-  </si>
-  <si>
-    <t>HERV1</t>
-  </si>
-  <si>
-    <t>herv1</t>
-  </si>
-  <si>
     <t>retrotector</t>
   </si>
   <si>
@@ -98,12 +83,6 @@
     <t>HERV19</t>
   </si>
   <si>
-    <t>HERV-24b</t>
-  </si>
-  <si>
-    <t>ERV24B_Prim</t>
-  </si>
-  <si>
     <t>HERV-31</t>
   </si>
   <si>
@@ -335,19 +314,91 @@
     <t>mer89</t>
   </si>
   <si>
-    <t>PRIMA-41</t>
-  </si>
-  <si>
-    <t>PRIMA41</t>
-  </si>
-  <si>
-    <t>prima41</t>
-  </si>
-  <si>
-    <t>PRIMA-X</t>
-  </si>
-  <si>
-    <t>PRIMAX</t>
+    <t>erv_lineage.name</t>
+  </si>
+  <si>
+    <t>ERVR-3.Lambda.16A3</t>
+  </si>
+  <si>
+    <t>ERV-3.Lambda.47</t>
+  </si>
+  <si>
+    <t>ERV-3.Lambda.Lb4</t>
+  </si>
+  <si>
+    <t>ERV-3.Lambda.16</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.19</t>
+  </si>
+  <si>
+    <t>ERV-1.Rho.Rb.31</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.35</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.W9P.P.G25</t>
+  </si>
+  <si>
+    <t>ERV-3.Lambda.40</t>
+  </si>
+  <si>
+    <t>ERV-3.Lambda.53</t>
+  </si>
+  <si>
+    <t>ERV-3.Lambda.74</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.W9P.P.1</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.W9P.P.2</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.LOR1</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.37</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.43</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.101</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.MER21</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.MER31</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.MER34b</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.MER41</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.MER57</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.MER61</t>
+  </si>
+  <si>
+    <t>ERVR-1.Unclassified.MER65</t>
+  </si>
+  <si>
+    <t>ERVR-3.Lambda.70</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.MER83A</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.MER83B</t>
+  </si>
+  <si>
+    <t>ERVR-1.Zeta.MER84</t>
   </si>
 </sst>
 </file>
@@ -371,7 +422,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,6 +432,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -397,9 +454,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -714,791 +772,840 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74414C0-0D01-9B4D-8A37-18FCBAAA5CE9}">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="C16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="C17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="E21" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="E22" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="C23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="C24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="C25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B26" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="C26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="C27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="C28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B29" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="B29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="E30" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B31" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="C31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B32" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D32" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B33" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="C33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="B34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B35" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="C35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B36" t="s">
-        <v>4</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B37" t="s">
-        <v>4</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="C37" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D37" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B38" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="C38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B39" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="E39" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D39" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="C40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B41" t="s">
-        <v>4</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="E41" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="C42" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B42" t="s">
-        <v>4</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="C43" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="E43" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B44" t="s">
-        <v>4</v>
-      </c>
-      <c r="C44" t="s">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" t="s">
-        <v>4</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D45" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="C45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B46" t="s">
-        <v>4</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="C46" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B47" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>88</v>
-      </c>
-      <c r="B48" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B48" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D48" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B49" t="s">
-        <v>4</v>
-      </c>
-      <c r="C49" t="s">
-        <v>93</v>
-      </c>
-      <c r="D49" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" t="s">
-        <v>4</v>
-      </c>
-      <c r="C50" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" t="s">
-        <v>96</v>
-      </c>
-      <c r="D51" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>97</v>
-      </c>
-      <c r="B52" t="s">
-        <v>4</v>
-      </c>
-      <c r="C52" t="s">
-        <v>98</v>
-      </c>
-      <c r="D52" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>97</v>
-      </c>
-      <c r="B53" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" t="s">
-        <v>99</v>
-      </c>
-      <c r="D53" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>100</v>
-      </c>
-      <c r="B54" t="s">
-        <v>4</v>
-      </c>
-      <c r="C54" t="s">
-        <v>101</v>
-      </c>
-      <c r="D54" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>100</v>
-      </c>
-      <c r="B55" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" t="s">
-        <v>102</v>
-      </c>
-      <c r="D55" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>103</v>
-      </c>
-      <c r="B56" t="s">
-        <v>4</v>
-      </c>
-      <c r="C56" t="s">
-        <v>104</v>
-      </c>
-      <c r="D56" t="s">
-        <v>6</v>
+      <c r="E49" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
